--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -20,13 +20,14 @@
     <sheet sheetId="14" name="13. タイムスタンプ未取得レビューに準備中メッセージを表示" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="14. SEO対策：titleタグ・meta descript" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="15. トップページにmeta descriptionを追加（" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="16. 「ホラー映画診断」ページを新設" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="159">
   <si>
     <t>日付</t>
   </si>
@@ -112,6 +113,12 @@
     <t>トップページにmeta descriptionを追加（掲載作品数を動的反映）</t>
   </si>
   <si>
+    <t>2026/10/12</t>
+  </si>
+  <si>
+    <t>「ホラー映画診断」ページを新設</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -473,6 +480,30 @@
   </si>
   <si>
     <t>検索結果スニペットの反映自体はGoogleの再クロール・キャッシュ更新のタイミング次第のため、即時反映を保証するものではない</t>
+  </si>
+  <si>
+    <t>2026/10/12　｜　変更の大きさ：中　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>5つの3択質問（びっくり度・グロ度・精神ダメージ・日常侵食度への耐性＋動物の安否）に答えると、全作品から「おすすめ1〜2本」と、苦手な軸だけ基準を1段階ゆるめた「背伸び枠」1本を診断する新ページ（/diagnosis/）を追加。ヘッダー・ドロワーナビに導線も追加。</t>
+  </si>
+  <si>
+    <t>レビュー一覧の絞り込み機能はあったが、「自分の耐性に合う作品」を能動的に選び出す導線がなく、初めて訪れたビビリなユーザーが何を観ればいいか判断しづらかった</t>
+  </si>
+  <si>
+    <t>4軸のうち「精神ダメージ」「日常侵食度」はreviews.js（一覧用の軽量データ）には含まれておらず、各レビュー詳細データ（fearCards）にしかない状態だった</t>
+  </si>
+  <si>
+    <t>診断ロジックは src/data/reviews/index.js（詳細データ）をビルド時に読み、診断に必要な項目だけを抽出した軽量データのみをクライアントに渡す設計にして、ページの転送量を抑えた</t>
+  </si>
+  <si>
+    <t>「弱い／普通／強い」の3択は、実測の点数分布（精神ダメージは4〜5点が全体の57%を占めるなど）をもとに弱い=2・普通=4・強い=5に対応付け、全243通りの回答パターンでおすすめ0件になるケースが出ないことを事前に検証</t>
+  </si>
+  <si>
+    <t>該当作品が0件の場合は最もマイルドな作品にフォールバックする救済ロジックも実装（今回の閾値設計では理論上到達しないが保険として残置）</t>
+  </si>
+  <si>
+    <t>実装中、サイト全体で使っているレスポンシブ規則（画面幅900px以上でレビューカードを3カラム表示にするCSS）が診断結果カードにも干渉してレイアウトが崩れる不具合を発見し、診断ページ側で優先度の高いセレクタを追加して解消</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1174,6 +1205,17 @@
       </c>
       <c r="C16" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1194,6 +1236,7 @@
     <hyperlink ref="B14" r:id="rId13" location="#'13. タイムスタンプ未取得レビューに準備中メッセージを表示'!A1"/>
     <hyperlink ref="B15" r:id="rId14" location="#'14. SEO対策：titleタグ・meta descript'!A1"/>
     <hyperlink ref="B16" r:id="rId15" location="#'15. トップページにmeta descriptionを追加（'!A1"/>
+    <hyperlink ref="B17" r:id="rId16" location="#'16. 「ホラー映画診断」ページを新設'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1217,76 +1260,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1324,76 +1367,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1431,76 +1474,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1538,76 +1581,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1645,68 +1688,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1744,100 +1787,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1875,68 +1918,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1951,6 +1994,121 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A16" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="11"/>
+    </row>
+    <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A18" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1974,100 +2132,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2105,68 +2263,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2204,124 +2362,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2359,92 +2517,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2482,68 +2640,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2581,92 +2739,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2704,76 +2862,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -2811,84 +2969,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -21,13 +21,14 @@
     <sheet sheetId="15" name="14. SEO対策：titleタグ・meta descript" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="15. トップページにmeta descriptionを追加（" state="visible" r:id="rId19"/>
     <sheet sheetId="17" name="16. 「ホラー映画診断」ページを新設" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="17. CLAUDE.mdのデータ構成・ソート順の記述を実装に" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="169">
   <si>
     <t>日付</t>
   </si>
@@ -119,6 +120,12 @@
     <t>「ホラー映画診断」ページを新設</t>
   </si>
   <si>
+    <t>2026/10/16</t>
+  </si>
+  <si>
+    <t>CLAUDE.mdのデータ構成・ソート順の記述を実装に合わせて修正</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -504,6 +511,30 @@
   </si>
   <si>
     <t>実装中、サイト全体で使っているレスポンシブ規則（画面幅900px以上でレビューカードを3カラム表示にするCSS）が診断結果カードにも干渉してレイアウトが崩れる不具合を発見し、診断ページ側で優先度の高いセレクタを追加して解消</t>
+  </si>
+  <si>
+    <t>2026/10/16　｜　変更の大きさ：小　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>CLAUDE.mdと.clauderules/review-schema.mdで、reviews.jsの役割と一覧ページの表示順の決まり方についての記述を、実際のコードの動きに合わせて書き直した。ディレクトリ構成にも、まとめ記事（articles）と診断ページ（diagnosis）を追加した。</t>
+  </si>
+  <si>
+    <t>メモには「reviews.jsの配列順＝一覧ページの表示順」と書かれていたが、実際の一覧ページはreviews/index.jsを読み込み、publishedAtの新しい順に並べ直して表示していた</t>
+  </si>
+  <si>
+    <t>reviews.jsは「一覧・フィルター用」とされていたが、実際には詳細ページ下部の「関連作品」でしか使われていなかった</t>
+  </si>
+  <si>
+    <t>メモと実装が食い違ったままだと、表示順を変えたいときに配列を並べ替えても反映されないなど、作業ミスにつながるおそれがあった</t>
+  </si>
+  <si>
+    <t>reviews.jsの用途（関連作品のみ）と、一覧の表示順はpublishedAtで決まること（同日公開の作品どうしは配列順）がメモに正しく記載された</t>
+  </si>
+  <si>
+    <t>ディレクトリ構成に、現在あるページ（まとめ記事・診断）がすべて載った</t>
+  </si>
+  <si>
+    <t>サイトの表示・動作には変更なし（ドキュメントのみの修正）</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1216,6 +1247,17 @@
       </c>
       <c r="C17" s="7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1237,6 +1279,7 @@
     <hyperlink ref="B15" r:id="rId14" location="#'14. SEO対策：titleタグ・meta descript'!A1"/>
     <hyperlink ref="B16" r:id="rId15" location="#'15. トップページにmeta descriptionを追加（'!A1"/>
     <hyperlink ref="B17" r:id="rId16" location="#'16. 「ホラー映画診断」ページを新設'!A1"/>
+    <hyperlink ref="B18" r:id="rId17" location="#'17. CLAUDE.mdのデータ構成・ソート順の記述を実装に'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1260,76 +1303,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1367,76 +1410,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1474,76 +1517,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1581,76 +1624,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1688,68 +1731,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1787,100 +1830,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1918,68 +1961,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2017,84 +2060,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="14"/>
     </row>
@@ -2105,6 +2148,121 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A18" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="11"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A18:B18"/>
   </mergeCells>
   <hyperlinks>
@@ -2132,100 +2290,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2263,68 +2421,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2362,124 +2520,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2517,92 +2675,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2640,68 +2798,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2739,92 +2897,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2862,76 +3020,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -2969,84 +3127,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -22,13 +22,14 @@
     <sheet sheetId="16" name="15. トップページにmeta descriptionを追加（" state="visible" r:id="rId19"/>
     <sheet sheetId="17" name="16. 「ホラー映画診断」ページを新設" state="visible" r:id="rId20"/>
     <sheet sheetId="18" name="17. CLAUDE.mdのデータ構成・ソート順の記述を実装に" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="18. レビューデータをContent Collections" state="visible" r:id="rId22"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="183">
   <si>
     <t>日付</t>
   </si>
@@ -126,6 +127,9 @@
     <t>CLAUDE.mdのデータ構成・ソート順の記述を実装に合わせて修正</t>
   </si>
   <si>
+    <t>レビューデータをContent Collections（YAML）に移行</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -535,6 +539,45 @@
   </si>
   <si>
     <t>サイトの表示・動作には変更なし（ドキュメントのみの修正）</t>
+  </si>
+  <si>
+    <t>2026/10/16　｜　変更の大きさ：中　｜　対象ツール：Claude Code</t>
+  </si>
+  <si>
+    <t>43作品のレビューデータを、JSファイル（src/data/reviews/*.js＋目次のindex.js＋関連作品用のreviews.js）から、AstroのContent Collections機能を使ったYAMLファイル（src/content/reviews/*.yaml）に移行した。データのルール（スキーマ）を src/content.config.js に定義し、ルールに合わないデータがあるとビルドがエラーで止まるようにした。あわせて CLAUDE.md と .clauderules/ の作業ルールを新しい手順に書き直した。</t>
+  </si>
+  <si>
+    <t>レビュー追加のたびに3ファイルを手で更新する必要があり、作品数が増えるほど手間と書き漏れのリスクが大きくなっていた</t>
+  </si>
+  <si>
+    <t>移行前の調査で、3ファイル間のずれがすでに発生していた（32作品で更新日、2作品でジャンルが不一致。reviews-list.csv も同様）</t>
+  </si>
+  <si>
+    <t>関連作品の計算に使う reviews.js に監督名がなく、「同じ監督の作品を優先する」処理が一度も働いていなかった</t>
+  </si>
+  <si>
+    <t>必須項目や値の形式のチェックを毎回目視で行っており、屋敷女の動物ラベルが「⚠️ 危険」（正しくは「❌ 危険」）のまま公開されていた</t>
+  </si>
+  <si>
+    <t>レビュー追加が「YAMLを1ファイル置くだけ」になり、目次への追記や3ファイル間の同期作業が不要になった</t>
+  </si>
+  <si>
+    <t>必須項目の欠落・スコアの範囲外・動物ラベルの不一致・日付形式・sortOrderの重複など15種類以上の誤りを、ビルド時に日本語のメッセージで検出できるようになった（わざと誤ったデータを入れて動作を確認済み）</t>
+  </si>
+  <si>
+    <t>変換前後のデータを全43作品で機械的に比較し、内容が完全に一致することを確認。移行前後で全48ページのHTMLを比較し、差は関連作品欄（12ページ）と屋敷女の動物ラベル修正のみであることを確認</t>
+  </si>
+  <si>
+    <t>関連作品で監督ボーナスが働くようになった（例：ヘレディタリーは関連作品が0件だったのが、ミッドサマー・ボーはおそれているが表示されるように）</t>
+  </si>
+  <si>
+    <t>同じ公開日の作品の並び順を固定するため sortOrder 項目を追加し、一覧の並び順は移行前と完全に同じに保った</t>
+  </si>
+  <si>
+    <t>reviews-list.csv の更新日・ジャンルのずれも詳細データに合わせて修正した</t>
+  </si>
+  <si>
+    <t>胸騒ぎ（munasawagi）の出演者が未記入であることが判明。人間から提供された情報で出演者を記入し、スキーマでも空欄を許可しない設定にした</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1258,6 +1301,17 @@
       </c>
       <c r="C18" s="8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1280,6 +1334,7 @@
     <hyperlink ref="B16" r:id="rId15" location="#'15. トップページにmeta descriptionを追加（'!A1"/>
     <hyperlink ref="B17" r:id="rId16" location="#'16. 「ホラー映画診断」ページを新設'!A1"/>
     <hyperlink ref="B18" r:id="rId17" location="#'17. CLAUDE.mdのデータ構成・ソート順の記述を実装に'!A1"/>
+    <hyperlink ref="B19" r:id="rId18" location="#'18. レビューデータをContent Collections'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1303,76 +1358,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1410,76 +1465,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1517,76 +1572,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1624,76 +1679,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1731,68 +1786,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1830,100 +1885,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -1961,68 +2016,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2060,84 +2115,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="14"/>
     </row>
@@ -2175,84 +2230,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="14"/>
     </row>
@@ -2267,6 +2322,161 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="126" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="11"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A23:B23"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A23" r:id="rId1" location="#'目次'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2290,100 +2500,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2421,68 +2631,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2520,124 +2730,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2675,92 +2885,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -2798,68 +3008,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2897,92 +3107,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -3020,76 +3230,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -3127,84 +3337,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="14"/>
     </row>

--- a/サイト改善ログ.xlsx
+++ b/サイト改善ログ.xlsx
@@ -23,13 +23,14 @@
     <sheet sheetId="17" name="16. 「ホラー映画診断」ページを新設" state="visible" r:id="rId20"/>
     <sheet sheetId="18" name="17. CLAUDE.mdのデータ構成・ソート順の記述を実装に" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="18. レビューデータをContent Collections" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="19. まとめ記事をContent Collections（M" state="visible" r:id="rId23"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="193">
   <si>
     <t>日付</t>
   </si>
@@ -130,6 +131,9 @@
     <t>レビューデータをContent Collections（YAML）に移行</t>
   </si>
   <si>
+    <t>まとめ記事をContent Collections（Markdown）に移行</t>
+  </si>
+  <si>
     <t>2026/06　｜　変更の大きさ：大　｜　対象ツール：手動</t>
   </si>
   <si>
@@ -578,6 +582,33 @@
   </si>
   <si>
     <t>胸騒ぎ（munasawagi）の出演者が未記入であることが判明。人間から提供された情報で出演者を記入し、スキーマでも空欄を許可しない設定にした</t>
+  </si>
+  <si>
+    <t>まとめ記事のデータを、JSファイル（src/data/articles.js）から、Content Collections を使った Markdown ファイル（src/content/articles/*.md）に移行した。タイトルや日付・おすすめ欄は先頭の項目欄に、イントロ・作品ごとの紹介文・総評は本文として「イントロ → ## 作品ID → ## 総評」の順で書く形にした。あわせて記事用の作業ルール（.clauderules/article-schema.md）を新設し、CLAUDE.md も更新した。</t>
+  </si>
+  <si>
+    <t>まとめ記事は長い文章が中心なのに、JSの文字列の中に「\n」で改行を書く必要があり、書きにくく読みにくかった</t>
+  </si>
+  <si>
+    <t>紹介する作品の一覧（filmIds）と作品ごとの紹介文（filmComments）が別々に管理されていて、片方だけ直すとずれる可能性があった</t>
+  </si>
+  <si>
+    <t>レビューを Content Collections に移行したことで、まとめ記事だけ古い方式のまま残っていた</t>
+  </si>
+  <si>
+    <t>本文を普通の文章として書けるようになった。改行はそのまま改行になり、**太字** などの Markdown 記法も使える</t>
+  </si>
+  <si>
+    <t>紹介する作品は「## 作品ID」の見出しだけで決まるようになり、一覧と紹介文のずれが起きない形になった</t>
+  </si>
+  <si>
+    <t>存在しない作品IDの見出し・総評の書き忘れ・おすすめ欄の作品が記事内にない、などの誤りをビルド時に日本語のメッセージで検出できるようになった（わざと誤ったデータを入れて動作を確認済み）</t>
+  </si>
+  <si>
+    <t>移行前後で全48ページのHTMLを比較し、差は記事ページの段落内の空白・改行位置のみで、表示は変わらないことを確認</t>
+  </si>
+  <si>
+    <t>Markdown の変換には Astro 本体が使っている @astrojs/markdown-remark を使い、package.json に依存関係として明記した</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="22" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1311,6 +1342,17 @@
         <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1335,6 +1377,7 @@
     <hyperlink ref="B17" r:id="rId16" location="#'16. 「ホラー映画診断」ページを新設'!A1"/>
     <hyperlink ref="B18" r:id="rId17" location="#'17. CLAUDE.mdのデータ構成・ソート順の記述を実装に'!A1"/>
     <hyperlink ref="B19" r:id="rId18" location="#'18. レビューデータをContent Collections'!A1"/>
+    <hyperlink ref="B20" r:id="rId19" location="#'19. まとめ記事をContent Collections（M'!A1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1358,76 +1401,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1465,76 +1508,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1572,76 +1615,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1679,76 +1722,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -1786,68 +1829,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1885,100 +1928,100 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2016,68 +2059,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2115,84 +2158,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="14"/>
     </row>
@@ -2230,84 +2273,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="72" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="14"/>
     </row>
@@ -2345,124 +2388,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="126" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="11"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2500,100 +2543,231 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="B20" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A20" r:id="rId1" location="#'目次'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="10"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="11"/>
+    </row>
+    <row r="5" ht="126" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="11"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>48</v>
       </c>
       <c r="B20" s="14"/>
     </row>
@@ -2631,68 +2805,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -2730,124 +2904,124 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="11"/>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="14"/>
     </row>
@@ -2885,92 +3059,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -3008,68 +3182,68 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -3107,92 +3281,92 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="14"/>
     </row>
@@ -3230,76 +3404,76 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="36" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14"/>
     </row>
@@ -3337,84 +3511,84 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B2" s="10"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="11"/>
     </row>
     <row r="5" ht="54" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="11"/>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11"/>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="14"/>
     </row>
